--- a/SGC-CKN/Excel/67d3c9c5-5450-44cb-bd0b-0082b7e3ca43_Lô_CT-02_P1-139_D800_25-01-2026.xlsx
+++ b/SGC-CKN/Excel/67d3c9c5-5450-44cb-bd0b-0082b7e3ca43_Lô_CT-02_P1-139_D800_25-01-2026.xlsx
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>SGC-KCN 0001</t>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>

--- a/SGC-CKN/Excel/67d3c9c5-5450-44cb-bd0b-0082b7e3ca43_Lô_CT-02_P1-139_D800_25-01-2026.xlsx
+++ b/SGC-CKN/Excel/67d3c9c5-5450-44cb-bd0b-0082b7e3ca43_Lô_CT-02_P1-139_D800_25-01-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>15:20 24/01/2026</t>
+    <t>15:20 24/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>01:45 25/01/2026</t>
+    <t>01:15 25/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">15:20
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:45
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:20
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:55
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">18:15
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:50
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>14</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:40
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>15</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">23:10
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>16</t>
@@ -175,8 +175,8 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">01:45
-25/01/2026</t>
+    <t xml:space="preserve">01:15
+25/03/2026</t>
   </si>
   <si>
     <t>Hố khoan chạm Sỏi Cuội -36,47 m</t>
@@ -1157,7 +1157,7 @@
         <v>0.42</v>
       </c>
       <c r="I11" s="5">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="J11" s="8">
         <v>2.5</v>
@@ -1399,13 +1399,13 @@
         <v>-44.269999999999996</v>
       </c>
       <c r="H18" s="28">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="I18" s="28">
         <v>10.12</v>
       </c>
       <c r="J18" s="8">
-        <v>3.92</v>
+        <v>4.86</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>52</v>
@@ -1569,10 +1569,10 @@
         <v>0.42</v>
       </c>
       <c r="H2" s="5">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="I2" s="8">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1769,13 +1769,13 @@
         <v>-44.27</v>
       </c>
       <c r="G9" s="28">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="H9" s="28">
         <v>10.12</v>
       </c>
       <c r="I9" s="8">
-        <v>3.92</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,13 +1798,13 @@
         <v>-44.27</v>
       </c>
       <c r="G10" s="33">
-        <v>10.42</v>
+        <v>9.92</v>
       </c>
       <c r="H10" s="33">
-        <v>44.27</v>
+        <v>43.56</v>
       </c>
       <c r="I10" s="33">
-        <v>4.25</v>
+        <v>4.39</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/67d3c9c5-5450-44cb-bd0b-0082b7e3ca43_Lô_CT-02_P1-139_D800_25-01-2026.xlsx
+++ b/SGC-CKN/Excel/67d3c9c5-5450-44cb-bd0b-0082b7e3ca43_Lô_CT-02_P1-139_D800_25-01-2026.xlsx
@@ -1186,16 +1186,16 @@
         <v>-1.75</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.85</v>
+        <v>-4.85</v>
       </c>
       <c r="H12" s="9">
         <v>0.58</v>
       </c>
       <c r="I12" s="9">
-        <v>8.1</v>
+        <v>3.1</v>
       </c>
       <c r="J12" s="12">
-        <v>13.89</v>
+        <v>5.31</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1218,19 +1218,19 @@
         <v>36</v>
       </c>
       <c r="F13" s="13">
-        <v>-9.85</v>
+        <v>-4.85</v>
       </c>
       <c r="G13" s="13">
-        <v>-18.15</v>
+        <v>-8.15</v>
       </c>
       <c r="H13" s="13">
         <v>0.58</v>
       </c>
       <c r="I13" s="13">
-        <v>8.3</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="12">
-        <v>14.23</v>
+        <v>5.66</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1253,19 +1253,19 @@
         <v>39</v>
       </c>
       <c r="F14" s="16">
-        <v>-18.15</v>
+        <v>-8.15</v>
       </c>
       <c r="G14" s="16">
-        <v>-22.15</v>
+        <v>-16.95</v>
       </c>
       <c r="H14" s="16">
         <v>1.33</v>
       </c>
       <c r="I14" s="16">
-        <v>4</v>
-      </c>
-      <c r="J14" s="8">
-        <v>3</v>
+        <v>8.8</v>
+      </c>
+      <c r="J14" s="12">
+        <v>6.6</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1288,19 +1288,19 @@
         <v>42</v>
       </c>
       <c r="F15" s="19">
+        <v>-16.95</v>
+      </c>
+      <c r="G15" s="19">
         <v>-22.15</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-26.15</v>
       </c>
       <c r="H15" s="19">
         <v>2.58</v>
       </c>
       <c r="I15" s="19">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="J15" s="8">
-        <v>1.55</v>
+        <v>2.01</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1323,10 +1323,10 @@
         <v>45</v>
       </c>
       <c r="F16" s="22">
+        <v>-22.15</v>
+      </c>
+      <c r="G16" s="22">
         <v>-26.15</v>
-      </c>
-      <c r="G16" s="22">
-        <v>-30.15</v>
       </c>
       <c r="H16" s="22">
         <v>0.83</v>
@@ -1358,10 +1358,10 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
+        <v>-26.15</v>
+      </c>
+      <c r="G17" s="25">
         <v>-30.15</v>
-      </c>
-      <c r="G17" s="25">
-        <v>-34.15</v>
       </c>
       <c r="H17" s="25">
         <v>1.5</v>
@@ -1393,19 +1393,19 @@
         <v>51</v>
       </c>
       <c r="F18" s="28">
-        <v>-34.15</v>
+        <v>-30.15</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.269999999999996</v>
+        <v>-40.25</v>
       </c>
       <c r="H18" s="28">
         <v>2.08</v>
       </c>
       <c r="I18" s="28">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="J18" s="8">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>52</v>
@@ -1592,16 +1592,16 @@
         <v>-1.75</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.85</v>
+        <v>-4.85</v>
       </c>
       <c r="G3" s="9">
         <v>0.58</v>
       </c>
       <c r="H3" s="9">
-        <v>8.1</v>
+        <v>3.1</v>
       </c>
       <c r="I3" s="12">
-        <v>13.89</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1618,19 +1618,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-9.85</v>
+        <v>-4.85</v>
       </c>
       <c r="F4" s="13">
-        <v>-18.15</v>
+        <v>-8.15</v>
       </c>
       <c r="G4" s="13">
         <v>0.58</v>
       </c>
       <c r="H4" s="13">
-        <v>8.3</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="12">
-        <v>14.23</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1647,19 +1647,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-18.15</v>
+        <v>-8.15</v>
       </c>
       <c r="F5" s="16">
-        <v>-22.15</v>
+        <v>-16.95</v>
       </c>
       <c r="G5" s="16">
         <v>1.33</v>
       </c>
       <c r="H5" s="16">
-        <v>4</v>
-      </c>
-      <c r="I5" s="8">
-        <v>3</v>
+        <v>8.8</v>
+      </c>
+      <c r="I5" s="12">
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1676,19 +1676,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
+        <v>-16.95</v>
+      </c>
+      <c r="F6" s="19">
         <v>-22.15</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-26.15</v>
       </c>
       <c r="G6" s="19">
         <v>2.58</v>
       </c>
       <c r="H6" s="19">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="I6" s="8">
-        <v>1.55</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1705,10 +1705,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
+        <v>-22.15</v>
+      </c>
+      <c r="F7" s="22">
         <v>-26.15</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-30.15</v>
       </c>
       <c r="G7" s="22">
         <v>0.83</v>
@@ -1734,10 +1734,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
+        <v>-26.15</v>
+      </c>
+      <c r="F8" s="25">
         <v>-30.15</v>
-      </c>
-      <c r="F8" s="25">
-        <v>-34.15</v>
       </c>
       <c r="G8" s="25">
         <v>1.5</v>
@@ -1763,19 +1763,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-34.15</v>
+        <v>-30.15</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.27</v>
+        <v>-40.25</v>
       </c>
       <c r="G9" s="28">
         <v>2.08</v>
       </c>
       <c r="H9" s="28">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="I9" s="8">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,16 +1795,16 @@
         <v>-0.71</v>
       </c>
       <c r="F10" s="33">
-        <v>-44.27</v>
+        <v>-40.25</v>
       </c>
       <c r="G10" s="33">
         <v>9.92</v>
       </c>
       <c r="H10" s="33">
-        <v>43.56</v>
+        <v>39.54</v>
       </c>
       <c r="I10" s="33">
-        <v>4.39</v>
+        <v>3.99</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/67d3c9c5-5450-44cb-bd0b-0082b7e3ca43_Lô_CT-02_P1-139_D800_25-01-2026.xlsx
+++ b/SGC-CKN/Excel/67d3c9c5-5450-44cb-bd0b-0082b7e3ca43_Lô_CT-02_P1-139_D800_25-01-2026.xlsx
@@ -1396,16 +1396,16 @@
         <v>-30.15</v>
       </c>
       <c r="G18" s="28">
-        <v>-40.25</v>
+        <v>-44.25</v>
       </c>
       <c r="H18" s="28">
         <v>2.08</v>
       </c>
       <c r="I18" s="28">
-        <v>10.1</v>
-      </c>
-      <c r="J18" s="8">
-        <v>4.85</v>
+        <v>14.1</v>
+      </c>
+      <c r="J18" s="12">
+        <v>6.77</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>52</v>
@@ -1766,16 +1766,16 @@
         <v>-30.15</v>
       </c>
       <c r="F9" s="28">
-        <v>-40.25</v>
+        <v>-44.25</v>
       </c>
       <c r="G9" s="28">
         <v>2.08</v>
       </c>
       <c r="H9" s="28">
-        <v>10.1</v>
-      </c>
-      <c r="I9" s="8">
-        <v>4.85</v>
+        <v>14.1</v>
+      </c>
+      <c r="I9" s="12">
+        <v>6.77</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,16 +1795,16 @@
         <v>-0.71</v>
       </c>
       <c r="F10" s="33">
-        <v>-40.25</v>
+        <v>-44.25</v>
       </c>
       <c r="G10" s="33">
         <v>9.92</v>
       </c>
       <c r="H10" s="33">
-        <v>39.54</v>
+        <v>43.54</v>
       </c>
       <c r="I10" s="33">
-        <v>3.99</v>
+        <v>4.39</v>
       </c>
     </row>
   </sheetData>
